--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-07-2025.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>£11.52</t>
+          <t>£11.15 Pre Sale Price-£11.99</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>£13.21</t>
+          <t>£12.80 Pre Sale Price-£13.99</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>£17.17</t>
+          <t>£15.99 Pre Sale Price-£17.99</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>£18.21 Pre Sale Price-£19.70</t>
+          <t>£16.70 Pre Sale Price-£19.99</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>£21.28</t>
+          <t>£21.20 Pre Sale Price-£21.99</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>£24.30</t>
+          <t>£23.13 Pre Sale Price-£24.99</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>£24.84 Pre Sale Price-£27.50</t>
+          <t>£23.50 Pre Sale Price-£25.99</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>£26.78 Pre Sale Price-£27.99</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>£30.53</t>
+          <t>£28.99 Pre Sale Price-£31.99</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>£30.42 Pre Sale Price-£34.99</t>
+          <t>£28.61 Pre Sale Price-£32.99</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>£39.13</t>
+          <t>£36.90 Pre Sale Price-£39.99</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>£37.13</t>
+          <t>£35.09 Pre Sale Price-£37.99</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>£44.43</t>
+          <t>£42.78 Pre Sale Price-£44.99</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>£47.07 Pre Sale Price-£54.99</t>
+          <t>£43.58 Pre Sale Price-£49.99</t>
         </is>
       </c>
     </row>
